--- a/MODELO.xlsx
+++ b/MODELO.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="29032026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29032026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -388,7 +388,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -406,24 +406,24 @@
       <nvPicPr>
         <cNvPr id="4068" name="Imagen 4067"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1079501" y="0"/>
           <a:ext cx="734218" cy="822777"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -447,24 +447,24 @@
       <nvPicPr>
         <cNvPr id="4069" name="Imagen 4068"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="16319500" y="1"/>
           <a:ext cx="726824" cy="814412"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -488,24 +488,24 @@
       <nvPicPr>
         <cNvPr id="5" name="Imagen 4067"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1079501" y="0"/>
           <a:ext cx="734218" cy="822777"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -529,24 +529,24 @@
       <nvPicPr>
         <cNvPr id="6" name="Imagen 4068"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="16319500" y="1"/>
           <a:ext cx="726824" cy="814412"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -570,24 +570,24 @@
       <nvPicPr>
         <cNvPr id="8" name="Imagen 4067"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1079501" y="0"/>
           <a:ext cx="734218" cy="822777"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -611,24 +611,24 @@
       <nvPicPr>
         <cNvPr id="9" name="Imagen 4068"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="16319500" y="1"/>
           <a:ext cx="726824" cy="814412"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1324,30 +1324,30 @@
     <row r="14" ht="32.25" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>235698</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>Juan alfredo valverde prooca</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>001002000145896</t>
+          <t>001002000145677</t>
         </is>
       </c>
       <c r="F14" s="32" t="n">
-        <v>56.33</v>
+        <v>56.96</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>GUAYAQUIL</t>
+          <t>PICHINCHA</t>
         </is>
       </c>
       <c r="H14" s="10" t="n"/>
@@ -1355,7 +1355,7 @@
     <row r="15" ht="32.25" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Lucho</t>
+          <t>Luisa</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1374,11 +1374,11 @@
         </is>
       </c>
       <c r="F15" s="32" t="n">
-        <v>56.96</v>
+        <v>56.33</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>JEP</t>
+          <t>GUAYAQUIL</t>
         </is>
       </c>
       <c r="H15" s="10" t="n"/>
@@ -1386,7 +1386,7 @@
     <row r="16" ht="32.25" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>589498</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Lucho</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="F16" s="32" t="n">
-        <v>56.23</v>
+        <v>56.96</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>JARDIN AZUAYO</t>
+          <t>JEP</t>
         </is>
       </c>
       <c r="H16" s="10" t="n"/>
@@ -1448,7 +1448,7 @@
     <row r="18" ht="32.25" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>589498</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1458,20 +1458,20 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Lucho</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>001002000148966</t>
+          <t>001002000145896</t>
         </is>
       </c>
       <c r="F18" s="32" t="n">
-        <v>96</v>
+        <v>56.23</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>JEP</t>
+          <t>JARDIN AZUAYO</t>
         </is>
       </c>
       <c r="H18" s="10" t="n"/>
@@ -1494,11 +1494,11 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>0010020001456666</t>
+          <t>001002000148966</t>
         </is>
       </c>
       <c r="F19" s="32" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1510,41 +1510,63 @@
     <row r="20" ht="32.25" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>2255</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Lucho</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>0010020001456666</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>JEP</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="32.25" customHeight="1">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>12356</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Leonn</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>0010020001458888</t>
         </is>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="F21" s="32" t="n">
         <v>55522</v>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>PICHINCHA</t>
         </is>
       </c>
-      <c r="H20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="32.25" customHeight="1">
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="9" t="n"/>
       <c r="H21" s="10" t="n"/>
     </row>
     <row r="22" ht="32.25" customHeight="1">

--- a/MODELO.xlsx
+++ b/MODELO.xlsx
@@ -1324,7 +1324,7 @@
     <row r="14" ht="32.25" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>235698</t>
+          <t>1584276</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1334,20 +1334,20 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Juan alfredo valverde prooca</t>
+          <t>Jazmin andrea julia</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>001002000145677</t>
+          <t>001002000123566</t>
         </is>
       </c>
       <c r="F14" s="32" t="n">
-        <v>56.96</v>
+        <v>26.89</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>PICHINCHA</t>
+          <t>JARDIN AZUAYO</t>
         </is>
       </c>
       <c r="H14" s="10" t="n"/>
@@ -1355,30 +1355,30 @@
     <row r="15" ht="32.25" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>235698</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>Juan alfredo valverde prooca</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>001002000145896</t>
+          <t>001002000145677</t>
         </is>
       </c>
       <c r="F15" s="32" t="n">
-        <v>56.33</v>
+        <v>56.96</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>GUAYAQUIL</t>
+          <t>PICHINCHA</t>
         </is>
       </c>
       <c r="H15" s="10" t="n"/>
@@ -1386,7 +1386,7 @@
     <row r="16" ht="32.25" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Lucho</t>
+          <t>Luisa</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="F16" s="32" t="n">
-        <v>56.96</v>
+        <v>56.33</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>JEP</t>
+          <t>GUAYAQUIL</t>
         </is>
       </c>
       <c r="H16" s="10" t="n"/>
@@ -1417,7 +1417,7 @@
     <row r="17" ht="32.25" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>589498</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Lucho</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="F17" s="32" t="n">
-        <v>56.23</v>
+        <v>56.96</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>JARDIN AZUAYO</t>
+          <t>JEP</t>
         </is>
       </c>
       <c r="H17" s="10" t="n"/>
@@ -1479,7 +1479,7 @@
     <row r="19" ht="32.25" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>589498</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1489,20 +1489,20 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Lucho</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>001002000148966</t>
+          <t>001002000145896</t>
         </is>
       </c>
       <c r="F19" s="32" t="n">
-        <v>96</v>
+        <v>56.23</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>JEP</t>
+          <t>JARDIN AZUAYO</t>
         </is>
       </c>
       <c r="H19" s="10" t="n"/>
@@ -1525,11 +1525,11 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>0010020001456666</t>
+          <t>001002000148966</t>
         </is>
       </c>
       <c r="F20" s="32" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1541,41 +1541,63 @@
     <row r="21" ht="32.25" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
         <is>
+          <t>2255</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Lucho</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>0010020001456666</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>JEP</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="32.25" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>12356</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Leonn</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>0010020001458888</t>
         </is>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F22" s="32" t="n">
         <v>55522</v>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>PICHINCHA</t>
         </is>
       </c>
-      <c r="H21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="32" t="n"/>
-      <c r="G22" s="9" t="n"/>
       <c r="H22" s="10" t="n"/>
     </row>
     <row r="23" ht="32.25" customHeight="1">
